--- a/public/samples/전도금신청서_2026년04월분_홍길동.xlsx
+++ b/public/samples/전도금신청서_2026년04월분_홍길동.xlsx
@@ -524,7 +524,7 @@
         <v>푸른한식</v>
       </c>
       <c r="P8" t="str">
-        <v>중식 : 홍길동, 김서연, 용역2</v>
+        <v>중식 : 홍길동, 김영호, 용역2</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         <v>카페온도</v>
       </c>
       <c r="P9" t="str">
-        <v>음료-홍길동, 김서연</v>
+        <v>음료-홍길동, 김영호</v>
       </c>
     </row>
     <row r="10">
@@ -695,7 +695,7 @@
         <v>카페온도</v>
       </c>
       <c r="P19" t="str">
-        <v>음료 : 김서연, 용역1인</v>
+        <v>음료 : 김영호, 용역1인</v>
       </c>
     </row>
     <row r="20">
